--- a/literature-review/initial-search/initial_search_topic3.xlsx
+++ b/literature-review/initial-search/initial_search_topic3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="1" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="1" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42877A-1AF9-41B0-8222-5AB882CD4B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA3D667-1E91-4F4C-93BA-6B90BFE4BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="972" windowWidth="26556" windowHeight="14496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="179">
   <si>
     <t>Eureka: Evaluating and understanding large foundation models</t>
   </si>
@@ -59,9 +59,6 @@
     <t>https://arxiv.org/abs/2406.18295</t>
   </si>
   <si>
-    <t>Evaluating the Utilities of Foundation Models in</t>
-  </si>
-  <si>
     <t>T Liu, K Li, Y Wang, H Li, H Zhao</t>
   </si>
   <si>
@@ -383,9 +380,6 @@
     <t>https://openreview.net/forum?id=rZlLfa81D8</t>
   </si>
   <si>
-    <t>… Model for Evaluating Water Acquisitions to Reduce Total Dissolved Solids in Walker Lake A technical report for National Fish and Wildlife Foundation, Walker …</t>
-  </si>
-  <si>
     <t>E Borgen, B Aylward, G Pohll, A McCoy…</t>
   </si>
   <si>
@@ -470,9 +464,6 @@
     <t>https://www.gmc-uk.org/-/media/documents/final-report-postukmedreview_pdf-101155712.pdf</t>
   </si>
   <si>
-    <t>… Prince William Sound. Exxon Valdez Oil Spill Restoration Project Final Report (Restoration Project 12120114-Q), Pacific Wildlife Foundation and Centre for …</t>
-  </si>
-  <si>
     <t>L Bowen, AK Miles, BE Ballachey…</t>
   </si>
   <si>
@@ -557,40 +548,35 @@
     <t>C Gomes, T Brunschwiler</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Papers matching at least 1 Inclusion criteria &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">not </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>any exclusion criteria</t>
-    </r>
-  </si>
-  <si>
     <t>3 Most relevant papers that have been added to the snowballing base set</t>
+  </si>
+  <si>
+    <t>A Simulation Model for Evaluating Water Acquisitions to Reduce Total Dissolved Solids in Walker Lake</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2403.17886</t>
+  </si>
+  <si>
+    <t>Long-term Monitoring: Lingering Oil  Evaluating Chronic Exposure of Harlequin Ducks and Sea Otters to Lingering Exxon Valdez Oil in Western Prince William Sound</t>
+  </si>
+  <si>
+    <t>Papers matching at least 1 Inclusion criteria &amp; not any exclusion criteria</t>
+  </si>
+  <si>
+    <t>Concept of evalution via downstream tasks is not described in detail</t>
+  </si>
+  <si>
+    <t>Focusses on multitask evaluation, lacks technical  description of specific downstream tasks</t>
+  </si>
+  <si>
+    <t>Downstream task performance evaluation is only explained in the context of other studies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,14 +586,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -676,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -724,6 +702,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="fill" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1028,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T48"/>
+  <dimension ref="A1:U48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.77734375" customWidth="1"/>
@@ -1041,104 +1026,102 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="I1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="Q2" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="11">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>0</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="6">
         <v>2024</v>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="6">
         <v>3</v>
       </c>
-      <c r="F3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="12" t="s">
+      <c r="F3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L3" s="15"/>
-      <c r="M3" s="14"/>
-      <c r="N3" s="14"/>
-      <c r="O3" s="14"/>
-      <c r="P3" s="14"/>
-      <c r="Q3" s="16"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="7"/>
     </row>
     <row r="4" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17">
@@ -1168,7 +1151,7 @@
       <c r="I4" s="21"/>
       <c r="J4" s="20"/>
       <c r="K4" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L4" s="21"/>
       <c r="M4" s="20"/>
@@ -1177,48 +1160,52 @@
       <c r="P4" s="20"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="14">
+        <v>2024</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="7"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="16"/>
     </row>
     <row r="6" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="20">
         <v>2024</v>
@@ -1230,15 +1217,15 @@
         <v>2</v>
       </c>
       <c r="G6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>16</v>
       </c>
       <c r="I6" s="21"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="20"/>
@@ -1247,52 +1234,54 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E7" s="6">
+        <v>21</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E7" s="14">
-        <v>21</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="16"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L7" s="10"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="14">
         <v>2024</v>
@@ -1304,15 +1293,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>23</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="14"/>
@@ -1326,10 +1315,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="D9" s="6">
         <v>2023</v>
@@ -1344,7 +1333,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="6"/>
@@ -1361,10 +1350,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="D10" s="14">
         <v>2024</v>
@@ -1379,12 +1368,12 @@
         <v>3</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="14"/>
@@ -1393,52 +1382,56 @@
       <c r="P10" s="14"/>
       <c r="Q10" s="16"/>
     </row>
-    <row r="11" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="14">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="14">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="16"/>
+      <c r="I11" s="10"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="10"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D12" s="6">
         <v>2024</v>
@@ -1447,13 +1440,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="6"/>
@@ -1470,10 +1463,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="D13" s="14">
         <v>2024</v>
@@ -1485,15 +1478,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
       <c r="K13" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="14"/>
@@ -1502,52 +1495,50 @@
       <c r="P13" s="14"/>
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A14" s="5">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="6">
+        <v>0</v>
+      </c>
+      <c r="F14" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="14">
-        <v>2024</v>
-      </c>
-      <c r="E14" s="14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="16"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="7"/>
     </row>
     <row r="15" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>12</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="D15" s="14">
         <v>2024</v>
@@ -1559,15 +1550,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="14"/>
@@ -1581,10 +1572,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="D16" s="6">
         <v>2024</v>
@@ -1596,10 +1587,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="6"/>
@@ -1611,52 +1602,56 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E17" s="6">
+        <v>6</v>
+      </c>
+      <c r="F17" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E17" s="14">
-        <v>6</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="H17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="10"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="10"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>15</v>
       </c>
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="6">
         <v>2024</v>
@@ -1668,32 +1663,32 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="10"/>
       <c r="M18" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" s="18" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
         <v>16</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D19" s="20">
         <v>2024</v>
@@ -1705,25 +1700,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>173</v>
+      </c>
       <c r="I19" s="22"/>
       <c r="K19" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L19" s="22"/>
       <c r="Q19" s="22"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>17</v>
       </c>
       <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="D20" s="6">
         <v>2023</v>
@@ -1735,10 +1732,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="6"/>
@@ -1750,15 +1747,15 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>18</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="6">
         <v>2024</v>
@@ -1770,32 +1767,32 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="10"/>
       <c r="M21" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>19</v>
       </c>
       <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="D22" s="6">
         <v>2023</v>
@@ -1807,72 +1804,79 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="10"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="N22" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="7"/>
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
-    </row>
-    <row r="23" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="U22" s="25"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="13" t="s">
+      <c r="I23" s="10"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L23" s="10"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="11">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="16"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
-        <v>21</v>
-      </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="14"/>
+      <c r="D24" s="14">
+        <v>2024</v>
+      </c>
       <c r="E24" s="14">
         <v>0</v>
       </c>
@@ -1880,15 +1884,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L24" s="15"/>
       <c r="M24" s="14"/>
@@ -1896,19 +1900,16 @@
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="16"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>22</v>
       </c>
       <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="D25" s="6">
         <v>2020</v>
@@ -1920,30 +1921,32 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="6"/>
+      <c r="M25" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>23</v>
       </c>
       <c r="B26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="D26" s="6">
         <v>2023</v>
@@ -1955,32 +1958,34 @@
         <v>2</v>
       </c>
       <c r="G26" t="s">
+        <v>84</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>85</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="I26" s="10"/>
       <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>167</v>
+      </c>
       <c r="L26" s="10"/>
       <c r="M26" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N26" s="6"/>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
       <c r="Q26" s="7"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>24</v>
       </c>
       <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="D27" s="6">
         <v>2005</v>
@@ -1992,32 +1997,32 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="10"/>
       <c r="M27" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>25</v>
       </c>
       <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="D28" s="6">
         <v>2021</v>
@@ -2029,10 +2034,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="6"/>
@@ -2046,56 +2051,58 @@
       <c r="R28"/>
       <c r="S28"/>
       <c r="T28"/>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="U28" s="25"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>26</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="6">
+        <v>0</v>
+      </c>
+      <c r="F29" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="14">
-        <v>2025</v>
-      </c>
-      <c r="E29" s="14">
-        <v>0</v>
-      </c>
-      <c r="F29" s="12" t="s">
+      <c r="G29" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="H29" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="15"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-    </row>
-    <row r="30" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="10"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="L29" s="10"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>27</v>
       </c>
       <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="D30" s="6">
         <v>2011</v>
@@ -2107,10 +2114,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="6"/>
@@ -2124,16 +2131,17 @@
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+      <c r="U30" s="25"/>
+    </row>
+    <row r="31" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="11">
         <v>28</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="D31" s="14">
         <v>2024</v>
@@ -2145,15 +2153,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="14"/>
       <c r="K31" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="14"/>
@@ -2161,19 +2169,16 @@
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="16"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-    </row>
-    <row r="32" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>29</v>
       </c>
       <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="D32" s="6">
         <v>2024</v>
@@ -2185,10 +2190,10 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="6"/>
@@ -2202,18 +2207,21 @@
       <c r="R32"/>
       <c r="S32"/>
       <c r="T32"/>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+      <c r="U32" s="25"/>
+    </row>
+    <row r="33" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11">
         <v>30</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="14"/>
+      <c r="D33" s="14">
+        <v>2024</v>
+      </c>
       <c r="E33" s="14">
         <v>1</v>
       </c>
@@ -2221,15 +2229,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="14"/>
@@ -2237,19 +2245,16 @@
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="16"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>116</v>
+      <c r="B34" s="24" t="s">
+        <v>172</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D34" s="6">
         <v>2014</v>
@@ -2258,13 +2263,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="6"/>
@@ -2276,15 +2281,15 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="7"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D35" s="6">
         <v>2024</v>
@@ -2293,13 +2298,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="6"/>
@@ -2311,15 +2316,15 @@
       <c r="P35" s="6"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" s="6">
         <v>2005</v>
@@ -2331,30 +2336,32 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="6"/>
+      <c r="M36" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D37" s="6">
         <v>2024</v>
@@ -2363,33 +2370,32 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="6"/>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D38" s="6">
         <v>1993</v>
@@ -2401,10 +2407,10 @@
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="6"/>
@@ -2416,28 +2422,30 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="D39" s="6">
+        <v>2019</v>
+      </c>
       <c r="E39" s="6">
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="6"/>
@@ -2449,15 +2457,15 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D40" s="6">
         <v>2017</v>
@@ -2466,46 +2474,50 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="6"/>
+      <c r="M40" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2022</v>
+      </c>
       <c r="E41" s="6">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="6"/>
@@ -2517,15 +2529,15 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D42" s="6">
         <v>2015</v>
@@ -2534,13 +2546,13 @@
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="6"/>
@@ -2552,27 +2564,28 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B44" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B45" s="18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/literature-review/initial-search/initial_search_topic3.xlsx
+++ b/literature-review/initial-search/initial_search_topic3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42877A-1AF9-41B0-8222-5AB882CD4B74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F31CEA-A453-4E75-BE1D-85C339A1213B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12660" yWindow="972" windowWidth="26556" windowHeight="14496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12288" yWindow="-15732" windowWidth="22956" windowHeight="13212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="179">
   <si>
     <t>Eureka: Evaluating and understanding large foundation models</t>
   </si>
@@ -59,9 +59,6 @@
     <t>https://arxiv.org/abs/2406.18295</t>
   </si>
   <si>
-    <t>Evaluating the Utilities of Foundation Models in</t>
-  </si>
-  <si>
     <t>T Liu, K Li, Y Wang, H Li, H Zhao</t>
   </si>
   <si>
@@ -383,9 +380,6 @@
     <t>https://openreview.net/forum?id=rZlLfa81D8</t>
   </si>
   <si>
-    <t>… Model for Evaluating Water Acquisitions to Reduce Total Dissolved Solids in Walker Lake A technical report for National Fish and Wildlife Foundation, Walker …</t>
-  </si>
-  <si>
     <t>E Borgen, B Aylward, G Pohll, A McCoy…</t>
   </si>
   <si>
@@ -470,9 +464,6 @@
     <t>https://www.gmc-uk.org/-/media/documents/final-report-postukmedreview_pdf-101155712.pdf</t>
   </si>
   <si>
-    <t>… Prince William Sound. Exxon Valdez Oil Spill Restoration Project Final Report (Restoration Project 12120114-Q), Pacific Wildlife Foundation and Centre for …</t>
-  </si>
-  <si>
     <t>L Bowen, AK Miles, BE Ballachey…</t>
   </si>
   <si>
@@ -557,40 +548,35 @@
     <t>C Gomes, T Brunschwiler</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Papers matching at least 1 Inclusion criteria &amp; </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">not </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>any exclusion criteria</t>
-    </r>
-  </si>
-  <si>
     <t>3 Most relevant papers that have been added to the snowballing base set</t>
+  </si>
+  <si>
+    <t>A Simulation Model for Evaluating Water Acquisitions to Reduce Total Dissolved Solids in Walker Lake</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2403.17886</t>
+  </si>
+  <si>
+    <t>Long-term Monitoring: Lingering Oil  Evaluating Chronic Exposure of Harlequin Ducks and Sea Otters to Lingering Exxon Valdez Oil in Western Prince William Sound</t>
+  </si>
+  <si>
+    <t>Papers matching at least 1 Inclusion criteria &amp; not any exclusion criteria</t>
+  </si>
+  <si>
+    <t>Concept of evalution via downstream tasks is not described in detail</t>
+  </si>
+  <si>
+    <t>Focusses on multitask evaluation, lacks technical  description of specific downstream tasks</t>
+  </si>
+  <si>
+    <t>Downstream task performance evaluation is only explained in the context of other studies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -600,14 +586,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -676,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -724,6 +702,26 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="fill" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="fill"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1029,81 +1027,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="60.77734375" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" style="8" customWidth="1"/>
-    <col min="4" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="8" customWidth="1"/>
-    <col min="9" max="16" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.7890625" customWidth="1"/>
+    <col min="2" max="2" width="60.7890625" customWidth="1"/>
+    <col min="3" max="3" width="30.7890625" style="8" customWidth="1"/>
+    <col min="4" max="7" width="10.7890625" customWidth="1"/>
+    <col min="8" max="8" width="10.7890625" style="8" customWidth="1"/>
+    <col min="9" max="16" width="8.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="I1" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="M1" s="2"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="M1" s="2"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="Q2" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11">
         <v>0</v>
       </c>
@@ -1131,7 +1129,7 @@
       <c r="I3" s="15"/>
       <c r="J3" s="14"/>
       <c r="K3" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L3" s="15"/>
       <c r="M3" s="14"/>
@@ -1140,7 +1138,7 @@
       <c r="P3" s="14"/>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="17">
         <v>1</v>
       </c>
@@ -1168,7 +1166,7 @@
       <c r="I4" s="21"/>
       <c r="J4" s="20"/>
       <c r="K4" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L4" s="21"/>
       <c r="M4" s="20"/>
@@ -1177,48 +1175,52 @@
       <c r="P4" s="20"/>
       <c r="Q4" s="22"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
+    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="11">
+        <v>2</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="D5" s="14">
+        <v>2024</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="6"/>
-      <c r="Q5" s="7"/>
-    </row>
-    <row r="6" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="15"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="L5" s="15"/>
+      <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
+      <c r="O5" s="14"/>
+      <c r="P5" s="14"/>
+      <c r="Q5" s="16"/>
+    </row>
+    <row r="6" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="17">
         <v>3</v>
       </c>
       <c r="B6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>13</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>14</v>
       </c>
       <c r="D6" s="20">
         <v>2024</v>
@@ -1230,15 +1232,15 @@
         <v>2</v>
       </c>
       <c r="G6" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>15</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>16</v>
       </c>
       <c r="I6" s="21"/>
       <c r="J6" s="20"/>
       <c r="K6" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L6" s="21"/>
       <c r="M6" s="20"/>
@@ -1247,52 +1249,54 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11">
+    <row r="7" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="25">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E7" s="28">
+        <v>21</v>
+      </c>
+      <c r="F7" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E7" s="14">
-        <v>21</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="H7" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L7" s="15"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="16"/>
-    </row>
-    <row r="8" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="29"/>
+      <c r="J7" s="28"/>
+      <c r="K7" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L7" s="29"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="30"/>
+    </row>
+    <row r="8" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="11">
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="D8" s="14">
         <v>2024</v>
@@ -1304,15 +1308,15 @@
         <v>2</v>
       </c>
       <c r="G8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="13" t="s">
         <v>22</v>
-      </c>
-      <c r="H8" s="13" t="s">
-        <v>23</v>
       </c>
       <c r="I8" s="15"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L8" s="15"/>
       <c r="M8" s="14"/>
@@ -1321,15 +1325,15 @@
       <c r="P8" s="14"/>
       <c r="Q8" s="16"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
         <v>6</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>25</v>
       </c>
       <c r="D9" s="6">
         <v>2023</v>
@@ -1344,7 +1348,7 @@
         <v>3</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I9" s="10"/>
       <c r="J9" s="6"/>
@@ -1356,15 +1360,15 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="7"/>
     </row>
-    <row r="10" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11">
         <v>7</v>
       </c>
       <c r="B10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="D10" s="14">
         <v>2024</v>
@@ -1379,12 +1383,12 @@
         <v>3</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="14"/>
       <c r="K10" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L10" s="15"/>
       <c r="M10" s="14"/>
@@ -1393,52 +1397,56 @@
       <c r="P10" s="14"/>
       <c r="Q10" s="16"/>
     </row>
-    <row r="11" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+    <row r="11" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" s="25">
         <v>8</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="D11" s="28">
+        <v>2024</v>
+      </c>
+      <c r="E11" s="28">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="H11" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="14">
-        <v>2024</v>
-      </c>
-      <c r="E11" s="14">
-        <v>0</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="H11" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L11" s="15"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14"/>
-      <c r="Q11" s="16"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="I11" s="29"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L11" s="29"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q11" s="30" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>34</v>
       </c>
       <c r="D12" s="6">
         <v>2024</v>
@@ -1447,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
+        <v>34</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="I12" s="10"/>
       <c r="J12" s="6"/>
@@ -1465,15 +1473,15 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="7"/>
     </row>
-    <row r="13" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11">
         <v>10</v>
       </c>
       <c r="B13" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" s="13" t="s">
         <v>37</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>38</v>
       </c>
       <c r="D13" s="14">
         <v>2024</v>
@@ -1485,15 +1493,15 @@
         <v>2</v>
       </c>
       <c r="G13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="I13" s="15"/>
       <c r="J13" s="14"/>
       <c r="K13" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L13" s="15"/>
       <c r="M13" s="14"/>
@@ -1502,52 +1510,52 @@
       <c r="P13" s="14"/>
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11">
+    <row r="14" spans="1:17" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="25">
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="28">
+        <v>2024</v>
+      </c>
+      <c r="E14" s="28">
+        <v>0</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="D14" s="14">
-        <v>2024</v>
-      </c>
-      <c r="E14" s="14">
-        <v>0</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="12" t="s">
+      <c r="H14" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L14" s="15"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
-      <c r="Q14" s="16"/>
-    </row>
-    <row r="15" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I14" s="29"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L14" s="29"/>
+      <c r="M14" s="28"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="30"/>
+    </row>
+    <row r="15" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="11">
         <v>12</v>
       </c>
       <c r="B15" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="D15" s="14">
         <v>2024</v>
@@ -1559,15 +1567,15 @@
         <v>2</v>
       </c>
       <c r="G15" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="14"/>
       <c r="K15" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L15" s="15"/>
       <c r="M15" s="14"/>
@@ -1576,15 +1584,15 @@
       <c r="P15" s="14"/>
       <c r="Q15" s="16"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5">
         <v>13</v>
       </c>
       <c r="B16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="D16" s="6">
         <v>2024</v>
@@ -1596,10 +1604,10 @@
         <v>2</v>
       </c>
       <c r="G16" t="s">
+        <v>50</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>52</v>
       </c>
       <c r="I16" s="10"/>
       <c r="J16" s="6"/>
@@ -1611,52 +1619,56 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="7"/>
     </row>
-    <row r="17" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11">
+    <row r="17" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="25">
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="D17" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E17" s="28">
+        <v>6</v>
+      </c>
+      <c r="F17" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="D17" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E17" s="14">
-        <v>6</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="H17" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L17" s="15"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
-      <c r="Q17" s="16"/>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I17" s="29"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L17" s="29"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q17" s="30" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5">
         <v>15</v>
       </c>
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>58</v>
       </c>
       <c r="D18" s="6">
         <v>2024</v>
@@ -1668,32 +1680,32 @@
         <v>2</v>
       </c>
       <c r="G18" t="s">
+        <v>58</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>59</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>60</v>
       </c>
       <c r="I18" s="10"/>
       <c r="J18" s="6"/>
       <c r="K18" s="6"/>
       <c r="L18" s="10"/>
       <c r="M18" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="7"/>
     </row>
-    <row r="19" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" s="18" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="17">
         <v>16</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D19" s="20">
         <v>2024</v>
@@ -1705,25 +1717,27 @@
         <v>2</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="H19" s="19"/>
+        <v>50</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>173</v>
+      </c>
       <c r="I19" s="22"/>
       <c r="K19" s="20" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L19" s="22"/>
       <c r="Q19" s="22"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5">
         <v>17</v>
       </c>
       <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>61</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>62</v>
       </c>
       <c r="D20" s="6">
         <v>2023</v>
@@ -1735,10 +1749,10 @@
         <v>2</v>
       </c>
       <c r="G20" t="s">
+        <v>62</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>63</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>64</v>
       </c>
       <c r="I20" s="10"/>
       <c r="J20" s="6"/>
@@ -1750,15 +1764,15 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="7"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="5">
         <v>18</v>
       </c>
       <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="D21" s="6">
         <v>2024</v>
@@ -1770,32 +1784,32 @@
         <v>2</v>
       </c>
       <c r="G21" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="8" t="s">
         <v>67</v>
-      </c>
-      <c r="H21" s="8" t="s">
-        <v>68</v>
       </c>
       <c r="I21" s="10"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="10"/>
       <c r="M21" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
       <c r="Q21" s="7"/>
     </row>
-    <row r="22" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5">
         <v>19</v>
       </c>
       <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>69</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>70</v>
       </c>
       <c r="D22" s="6">
         <v>2023</v>
@@ -1807,17 +1821,19 @@
         <v>2</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I22" s="10"/>
       <c r="J22" s="6"/>
       <c r="K22" s="6"/>
       <c r="L22" s="10"/>
       <c r="M22" s="6"/>
-      <c r="N22" s="6"/>
+      <c r="N22" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="7"/>
@@ -1825,54 +1841,58 @@
       <c r="S22"/>
       <c r="T22"/>
     </row>
-    <row r="23" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+    <row r="23" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="25">
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="D23" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E23" s="28">
+        <v>0</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="H23" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H23" s="13" t="s">
+      <c r="I23" s="29"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L23" s="29"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="30"/>
+    </row>
+    <row r="24" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="11">
+        <v>21</v>
+      </c>
+      <c r="B24" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="I23" s="15"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L23" s="15"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
-      <c r="Q23" s="16"/>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
-        <v>21</v>
-      </c>
-      <c r="B24" s="12" t="s">
+      <c r="C24" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="14"/>
+      <c r="D24" s="14">
+        <v>2024</v>
+      </c>
       <c r="E24" s="14">
         <v>0</v>
       </c>
@@ -1880,15 +1900,15 @@
         <v>2</v>
       </c>
       <c r="G24" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="13" t="s">
         <v>77</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>78</v>
       </c>
       <c r="I24" s="15"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L24" s="15"/>
       <c r="M24" s="14"/>
@@ -1896,19 +1916,16 @@
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="16"/>
-      <c r="R24" s="12"/>
-      <c r="S24" s="12"/>
-      <c r="T24" s="12"/>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5">
         <v>22</v>
       </c>
       <c r="B25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="D25" s="6">
         <v>2020</v>
@@ -1920,67 +1937,71 @@
         <v>2</v>
       </c>
       <c r="G25" t="s">
+        <v>80</v>
+      </c>
+      <c r="H25" s="8" t="s">
         <v>81</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>82</v>
       </c>
       <c r="I25" s="10"/>
       <c r="J25" s="6"/>
       <c r="K25" s="6"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="6"/>
+      <c r="M25" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N25" s="6"/>
       <c r="O25" s="6"/>
       <c r="P25" s="6"/>
       <c r="Q25" s="7"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+    <row r="26" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="25">
         <v>23</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B26" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="28">
+        <v>2023</v>
+      </c>
+      <c r="E26" s="28">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="6">
-        <v>2023</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" t="s">
+      <c r="H26" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="I26" s="10"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="N26" s="6"/>
-      <c r="O26" s="6"/>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="7"/>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="I26" s="29"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L26" s="29"/>
+      <c r="M26" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="30"/>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5">
         <v>24</v>
       </c>
       <c r="B27" t="s">
+        <v>86</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>88</v>
       </c>
       <c r="D27" s="6">
         <v>2005</v>
@@ -1992,32 +2013,32 @@
         <v>2</v>
       </c>
       <c r="G27" t="s">
+        <v>88</v>
+      </c>
+      <c r="H27" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="H27" s="8" t="s">
-        <v>90</v>
       </c>
       <c r="I27" s="10"/>
       <c r="J27" s="6"/>
       <c r="K27" s="6"/>
       <c r="L27" s="10"/>
       <c r="M27" s="6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6"/>
       <c r="P27" s="6"/>
       <c r="Q27" s="7"/>
     </row>
-    <row r="28" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5">
         <v>25</v>
       </c>
       <c r="B28" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="D28" s="6">
         <v>2021</v>
@@ -2029,10 +2050,10 @@
         <v>2</v>
       </c>
       <c r="G28" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="I28" s="10"/>
       <c r="J28" s="6"/>
@@ -2047,55 +2068,56 @@
       <c r="S28"/>
       <c r="T28"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="5">
+    <row r="29" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="25">
         <v>26</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="D29" s="28">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="28">
+        <v>0</v>
+      </c>
+      <c r="F29" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="D29" s="14">
-        <v>2025</v>
-      </c>
-      <c r="E29" s="14">
-        <v>0</v>
-      </c>
-      <c r="F29" s="12" t="s">
+      <c r="G29" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="H29" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="H29" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="15"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="L29" s="15"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="12"/>
-      <c r="S29" s="12"/>
-      <c r="T29" s="12"/>
-    </row>
-    <row r="30" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="I29" s="29"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L29" s="29"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q29" s="30" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="5">
         <v>27</v>
       </c>
       <c r="B30" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>101</v>
       </c>
       <c r="D30" s="6">
         <v>2011</v>
@@ -2107,10 +2129,10 @@
         <v>2</v>
       </c>
       <c r="G30" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>102</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>103</v>
       </c>
       <c r="I30" s="10"/>
       <c r="J30" s="6"/>
@@ -2125,15 +2147,15 @@
       <c r="S30"/>
       <c r="T30"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="5">
+    <row r="31" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="11">
         <v>28</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="C31" s="13" t="s">
         <v>104</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>105</v>
       </c>
       <c r="D31" s="14">
         <v>2024</v>
@@ -2145,15 +2167,15 @@
         <v>2</v>
       </c>
       <c r="G31" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>106</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>107</v>
       </c>
       <c r="I31" s="15"/>
       <c r="J31" s="14"/>
       <c r="K31" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L31" s="15"/>
       <c r="M31" s="14"/>
@@ -2161,19 +2183,16 @@
       <c r="O31" s="14"/>
       <c r="P31" s="14"/>
       <c r="Q31" s="16"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-    </row>
-    <row r="32" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:20" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="5">
         <v>29</v>
       </c>
       <c r="B32" t="s">
+        <v>107</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>108</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>109</v>
       </c>
       <c r="D32" s="6">
         <v>2024</v>
@@ -2185,10 +2204,10 @@
         <v>2</v>
       </c>
       <c r="G32" t="s">
+        <v>109</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>110</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>111</v>
       </c>
       <c r="I32" s="10"/>
       <c r="J32" s="6"/>
@@ -2203,17 +2222,19 @@
       <c r="S32"/>
       <c r="T32"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" s="5">
+    <row r="33" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="11">
         <v>30</v>
       </c>
       <c r="B33" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D33" s="14"/>
+      <c r="D33" s="14">
+        <v>2024</v>
+      </c>
       <c r="E33" s="14">
         <v>1</v>
       </c>
@@ -2221,15 +2242,15 @@
         <v>2</v>
       </c>
       <c r="G33" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>114</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>115</v>
       </c>
       <c r="I33" s="15"/>
       <c r="J33" s="14"/>
       <c r="K33" s="14" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L33" s="15"/>
       <c r="M33" s="14"/>
@@ -2237,19 +2258,16 @@
       <c r="O33" s="14"/>
       <c r="P33" s="14"/>
       <c r="Q33" s="16"/>
-      <c r="R33" s="12"/>
-      <c r="S33" s="12"/>
-      <c r="T33" s="12"/>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="5">
         <v>31</v>
       </c>
-      <c r="B34" t="s">
-        <v>116</v>
+      <c r="B34" s="24" t="s">
+        <v>172</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D34" s="6">
         <v>2014</v>
@@ -2258,13 +2276,13 @@
         <v>0</v>
       </c>
       <c r="F34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I34" s="10"/>
       <c r="J34" s="6"/>
@@ -2276,15 +2294,15 @@
       <c r="P34" s="6"/>
       <c r="Q34" s="7"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="5">
         <v>32</v>
       </c>
       <c r="B35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D35" s="6">
         <v>2024</v>
@@ -2293,13 +2311,13 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I35" s="10"/>
       <c r="J35" s="6"/>
@@ -2311,15 +2329,15 @@
       <c r="P35" s="6"/>
       <c r="Q35" s="7"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="5">
         <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D36" s="6">
         <v>2005</v>
@@ -2331,30 +2349,32 @@
         <v>2</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="I36" s="10"/>
       <c r="J36" s="6"/>
       <c r="K36" s="6"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="6"/>
+      <c r="M36" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N36" s="6"/>
       <c r="O36" s="6"/>
       <c r="P36" s="6"/>
       <c r="Q36" s="7"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="5">
         <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D37" s="6">
         <v>2024</v>
@@ -2363,33 +2383,32 @@
         <v>0</v>
       </c>
       <c r="F37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="I37" s="10"/>
       <c r="J37" s="6"/>
       <c r="K37" s="6"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="6"/>
       <c r="N37" s="6"/>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
       <c r="Q37" s="7"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="5">
         <v>35</v>
       </c>
       <c r="B38" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D38" s="6">
         <v>1993</v>
@@ -2401,10 +2420,10 @@
         <v>2</v>
       </c>
       <c r="G38" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="I38" s="10"/>
       <c r="J38" s="6"/>
@@ -2416,28 +2435,30 @@
       <c r="P38" s="6"/>
       <c r="Q38" s="7"/>
     </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="5">
         <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="6"/>
+        <v>132</v>
+      </c>
+      <c r="D39" s="6">
+        <v>2019</v>
+      </c>
       <c r="E39" s="6">
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="I39" s="10"/>
       <c r="J39" s="6"/>
@@ -2449,15 +2470,15 @@
       <c r="P39" s="6"/>
       <c r="Q39" s="7"/>
     </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="5">
         <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D40" s="6">
         <v>2017</v>
@@ -2466,46 +2487,50 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="I40" s="10"/>
       <c r="J40" s="6"/>
       <c r="K40" s="6"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="6"/>
+      <c r="M40" s="6" t="s">
+        <v>168</v>
+      </c>
       <c r="N40" s="6"/>
       <c r="O40" s="6"/>
       <c r="P40" s="6"/>
       <c r="Q40" s="7"/>
     </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="5">
         <v>38</v>
       </c>
       <c r="B41" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D41" s="6"/>
+        <v>140</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2022</v>
+      </c>
       <c r="E41" s="6">
         <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I41" s="10"/>
       <c r="J41" s="6"/>
@@ -2517,15 +2542,15 @@
       <c r="P41" s="6"/>
       <c r="Q41" s="7"/>
     </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="5">
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>145</v>
+        <v>174</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D42" s="6">
         <v>2015</v>
@@ -2534,13 +2559,13 @@
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="I42" s="10"/>
       <c r="J42" s="6"/>
@@ -2552,27 +2577,28 @@
       <c r="P42" s="6"/>
       <c r="Q42" s="7"/>
     </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="18" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/literature-review/initial-search/initial_search_topic3.xlsx
+++ b/literature-review/initial-search/initial_search_topic3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA3D667-1E91-4F4C-93BA-6B90BFE4BD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6500A9-FB03-4137-B8F4-C1F753DB9592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -654,7 +654,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -708,7 +708,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1823,7 +1822,7 @@
       <c r="R22"/>
       <c r="S22"/>
       <c r="T22"/>
-      <c r="U22" s="25"/>
+      <c r="U22"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
@@ -2051,7 +2050,7 @@
       <c r="R28"/>
       <c r="S28"/>
       <c r="T28"/>
-      <c r="U28" s="25"/>
+      <c r="U28"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
@@ -2131,7 +2130,7 @@
       <c r="R30"/>
       <c r="S30"/>
       <c r="T30"/>
-      <c r="U30" s="25"/>
+      <c r="U30"/>
     </row>
     <row r="31" spans="1:21" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
@@ -2207,7 +2206,7 @@
       <c r="R32"/>
       <c r="S32"/>
       <c r="T32"/>
-      <c r="U32" s="25"/>
+      <c r="U32"/>
     </row>
     <row r="33" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
